--- a/data/inventario.xlsx
+++ b/data/inventario.xlsx
@@ -427,7 +427,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>122000</v>
@@ -447,7 +447,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C3">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D3">
         <v>70000</v>
@@ -467,7 +467,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C4">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <v>108000</v>
@@ -487,7 +487,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C5">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>110000</v>
@@ -507,7 +507,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C6">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <v>56000</v>
@@ -527,7 +527,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C7">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D7">
         <v>88000</v>
@@ -567,7 +567,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9">
         <v>100000</v>
@@ -587,7 +587,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C10">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D10">
         <v>54000</v>
@@ -607,7 +607,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C11">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D11">
         <v>86000</v>
@@ -687,7 +687,7 @@
         <v>Rones</v>
       </c>
       <c r="C15">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D15">
         <v>78000</v>
@@ -707,7 +707,7 @@
         <v>Rones</v>
       </c>
       <c r="C16">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D16">
         <v>132000</v>
@@ -727,7 +727,7 @@
         <v>Rones</v>
       </c>
       <c r="C17">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17">
         <v>110000</v>
@@ -747,7 +747,7 @@
         <v>Rones</v>
       </c>
       <c r="C18">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D18">
         <v>68000</v>
@@ -787,7 +787,7 @@
         <v>Rones</v>
       </c>
       <c r="C20">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D20">
         <v>38000</v>
@@ -827,7 +827,7 @@
         <v>Brandy</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22">
         <v>78000</v>
@@ -847,7 +847,7 @@
         <v>Cervezas</v>
       </c>
       <c r="C23">
-        <v>144</v>
+        <v>54</v>
       </c>
       <c r="D23">
         <v>10000</v>
@@ -867,7 +867,7 @@
         <v>Cervezas</v>
       </c>
       <c r="C24">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="D24">
         <v>10000</v>
@@ -907,7 +907,7 @@
         <v>Cervezas</v>
       </c>
       <c r="C26">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D26">
         <v>10000</v>
@@ -967,7 +967,7 @@
         <v>Hidratantes</v>
       </c>
       <c r="C29">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D29">
         <v>6000</v>
@@ -1007,7 +1007,7 @@
         <v>Gaseosas</v>
       </c>
       <c r="C31">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D31">
         <v>5000</v>
@@ -1067,7 +1067,7 @@
         <v>Gaseosas</v>
       </c>
       <c r="C34">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D34">
         <v>5000</v>
@@ -1127,7 +1127,7 @@
         <v>Gaseosas</v>
       </c>
       <c r="C37">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D37">
         <v>5000</v>
@@ -1147,7 +1147,7 @@
         <v>Gaseosas</v>
       </c>
       <c r="C38">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D38">
         <v>5000</v>
@@ -1167,7 +1167,7 @@
         <v>Cervezas</v>
       </c>
       <c r="C39">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D39">
         <v>10000</v>

--- a/data/inventario.xlsx
+++ b/data/inventario.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,7 +427,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D2">
         <v>122000</v>
@@ -447,7 +447,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C3">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D3">
         <v>70000</v>
@@ -467,7 +467,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C4">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D4">
         <v>108000</v>
@@ -487,7 +487,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>110000</v>
@@ -507,7 +507,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D6">
         <v>56000</v>
@@ -527,7 +527,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C7">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="D7">
         <v>88000</v>
@@ -547,7 +547,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C8">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D8">
         <v>36000</v>
@@ -567,7 +567,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="D9">
         <v>100000</v>
@@ -587,7 +587,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C10">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>54000</v>
@@ -607,7 +607,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C11">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D11">
         <v>86000</v>
@@ -627,7 +627,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C12">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D12">
         <v>36000</v>
@@ -647,7 +647,7 @@
         <v>Rones</v>
       </c>
       <c r="C13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13">
         <v>88000</v>
@@ -667,7 +667,7 @@
         <v>Rones</v>
       </c>
       <c r="C14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14">
         <v>156000</v>
@@ -687,7 +687,7 @@
         <v>Rones</v>
       </c>
       <c r="C15">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D15">
         <v>78000</v>
@@ -707,7 +707,7 @@
         <v>Rones</v>
       </c>
       <c r="C16">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D16">
         <v>132000</v>
@@ -747,7 +747,7 @@
         <v>Rones</v>
       </c>
       <c r="C18">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D18">
         <v>68000</v>
@@ -767,7 +767,7 @@
         <v>Rones</v>
       </c>
       <c r="C19">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D19">
         <v>104000</v>
@@ -787,7 +787,7 @@
         <v>Rones</v>
       </c>
       <c r="C20">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D20">
         <v>38000</v>
@@ -847,7 +847,7 @@
         <v>Cervezas</v>
       </c>
       <c r="C23">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="D23">
         <v>10000</v>
@@ -867,7 +867,7 @@
         <v>Cervezas</v>
       </c>
       <c r="C24">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="D24">
         <v>10000</v>
@@ -887,7 +887,7 @@
         <v>Cervezas</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D25">
         <v>12000</v>
@@ -907,7 +907,7 @@
         <v>Cervezas</v>
       </c>
       <c r="C26">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D26">
         <v>10000</v>
@@ -967,7 +967,7 @@
         <v>Hidratantes</v>
       </c>
       <c r="C29">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="D29">
         <v>6000</v>
@@ -987,7 +987,7 @@
         <v>Hidratantes</v>
       </c>
       <c r="C30">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D30">
         <v>10000</v>
@@ -1007,7 +1007,7 @@
         <v>Gaseosas</v>
       </c>
       <c r="C31">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="D31">
         <v>5000</v>
@@ -1027,7 +1027,7 @@
         <v>Otros</v>
       </c>
       <c r="C32">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="D32">
         <v>5000</v>
@@ -1047,7 +1047,7 @@
         <v>Otros</v>
       </c>
       <c r="C33">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="D33">
         <v>3000</v>
@@ -1067,7 +1067,7 @@
         <v>Gaseosas</v>
       </c>
       <c r="C34">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D34">
         <v>5000</v>
@@ -1087,7 +1087,7 @@
         <v>Cervezas</v>
       </c>
       <c r="C35">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D35">
         <v>12000</v>
@@ -1107,7 +1107,7 @@
         <v>Cervezas</v>
       </c>
       <c r="C36">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D36">
         <v>12000</v>
@@ -1127,7 +1127,7 @@
         <v>Gaseosas</v>
       </c>
       <c r="C37">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D37">
         <v>5000</v>
@@ -1147,7 +1147,7 @@
         <v>Gaseosas</v>
       </c>
       <c r="C38">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D38">
         <v>5000</v>
@@ -1207,7 +1207,7 @@
         <v>Otros</v>
       </c>
       <c r="C41">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D41">
         <v>3000</v>
@@ -1259,9 +1259,29 @@
         <v>0</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Descorche</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Ingresos Barra</v>
+      </c>
+      <c r="C44">
+        <v>9998</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44" t="str">
+        <v>3/23/2026</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F43"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F44"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/inventario.xlsx
+++ b/data/inventario.xlsx
@@ -427,7 +427,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2">
         <v>122000</v>
@@ -447,7 +447,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C3">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D3">
         <v>70000</v>
@@ -467,7 +467,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C4">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D4">
         <v>108000</v>
@@ -487,7 +487,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <v>110000</v>
@@ -507,7 +507,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C6">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D6">
         <v>56000</v>
@@ -527,7 +527,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C7">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D7">
         <v>88000</v>
@@ -547,7 +547,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C8">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D8">
         <v>36000</v>
@@ -567,7 +567,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C9">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D9">
         <v>100000</v>
@@ -587,7 +587,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C10">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D10">
         <v>54000</v>
@@ -607,7 +607,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C11">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>86000</v>
@@ -627,7 +627,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C12">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D12">
         <v>36000</v>
@@ -647,7 +647,7 @@
         <v>Rones</v>
       </c>
       <c r="C13">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D13">
         <v>88000</v>
@@ -667,7 +667,7 @@
         <v>Rones</v>
       </c>
       <c r="C14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D14">
         <v>156000</v>
@@ -687,7 +687,7 @@
         <v>Rones</v>
       </c>
       <c r="C15">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D15">
         <v>78000</v>
@@ -707,7 +707,7 @@
         <v>Rones</v>
       </c>
       <c r="C16">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D16">
         <v>132000</v>
@@ -727,7 +727,7 @@
         <v>Rones</v>
       </c>
       <c r="C17">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D17">
         <v>110000</v>
@@ -747,7 +747,7 @@
         <v>Rones</v>
       </c>
       <c r="C18">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D18">
         <v>68000</v>
@@ -767,7 +767,7 @@
         <v>Rones</v>
       </c>
       <c r="C19">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D19">
         <v>104000</v>
@@ -847,7 +847,7 @@
         <v>Cervezas</v>
       </c>
       <c r="C23">
-        <v>64</v>
+        <v>146</v>
       </c>
       <c r="D23">
         <v>10000</v>
@@ -867,7 +867,7 @@
         <v>Cervezas</v>
       </c>
       <c r="C24">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D24">
         <v>10000</v>
@@ -887,10 +887,10 @@
         <v>Cervezas</v>
       </c>
       <c r="C25">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D25">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="E25" t="str">
         <v>10/2/2026</v>
@@ -907,7 +907,7 @@
         <v>Cervezas</v>
       </c>
       <c r="C26">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="D26">
         <v>10000</v>
@@ -947,7 +947,7 @@
         <v>Whisky</v>
       </c>
       <c r="C28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28">
         <v>74000</v>
@@ -967,7 +967,7 @@
         <v>Hidratantes</v>
       </c>
       <c r="C29">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D29">
         <v>6000</v>
@@ -987,7 +987,7 @@
         <v>Hidratantes</v>
       </c>
       <c r="C30">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D30">
         <v>10000</v>
@@ -1007,7 +1007,7 @@
         <v>Gaseosas</v>
       </c>
       <c r="C31">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D31">
         <v>5000</v>
@@ -1027,7 +1027,7 @@
         <v>Otros</v>
       </c>
       <c r="C32">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="D32">
         <v>5000</v>
@@ -1047,7 +1047,7 @@
         <v>Otros</v>
       </c>
       <c r="C33">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="D33">
         <v>3000</v>
@@ -1067,7 +1067,7 @@
         <v>Gaseosas</v>
       </c>
       <c r="C34">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="D34">
         <v>5000</v>
@@ -1087,7 +1087,7 @@
         <v>Cervezas</v>
       </c>
       <c r="C35">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D35">
         <v>12000</v>
@@ -1107,7 +1107,7 @@
         <v>Cervezas</v>
       </c>
       <c r="C36">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D36">
         <v>12000</v>
@@ -1127,7 +1127,7 @@
         <v>Gaseosas</v>
       </c>
       <c r="C37">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="D37">
         <v>5000</v>
@@ -1187,7 +1187,7 @@
         <v>Otros</v>
       </c>
       <c r="C40">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D40">
         <v>60000</v>
@@ -1207,7 +1207,7 @@
         <v>Otros</v>
       </c>
       <c r="C41">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D41">
         <v>3000</v>
@@ -1267,7 +1267,7 @@
         <v>Ingresos Barra</v>
       </c>
       <c r="C44">
-        <v>9998</v>
+        <v>9996</v>
       </c>
       <c r="D44">
         <v>0</v>

--- a/data/inventario.xlsx
+++ b/data/inventario.xlsx
@@ -427,7 +427,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D2">
         <v>122000</v>
@@ -447,7 +447,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C3">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="D3">
         <v>70000</v>
@@ -467,7 +467,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C4">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D4">
         <v>108000</v>
@@ -487,7 +487,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5">
         <v>110000</v>
@@ -507,7 +507,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C6">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D6">
         <v>56000</v>
@@ -527,7 +527,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C7">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D7">
         <v>88000</v>
@@ -547,7 +547,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D8">
         <v>36000</v>
@@ -567,7 +567,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C9">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D9">
         <v>100000</v>
@@ -587,7 +587,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10">
         <v>54000</v>
@@ -607,7 +607,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C11">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D11">
         <v>86000</v>
@@ -627,7 +627,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C12">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D12">
         <v>36000</v>
@@ -647,7 +647,7 @@
         <v>Rones</v>
       </c>
       <c r="C13">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D13">
         <v>88000</v>
@@ -687,7 +687,7 @@
         <v>Rones</v>
       </c>
       <c r="C15">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D15">
         <v>78000</v>
@@ -707,7 +707,7 @@
         <v>Rones</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D16">
         <v>132000</v>
@@ -727,7 +727,7 @@
         <v>Rones</v>
       </c>
       <c r="C17">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D17">
         <v>110000</v>
@@ -747,7 +747,7 @@
         <v>Rones</v>
       </c>
       <c r="C18">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D18">
         <v>68000</v>
@@ -767,7 +767,7 @@
         <v>Rones</v>
       </c>
       <c r="C19">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D19">
         <v>104000</v>
@@ -787,7 +787,7 @@
         <v>Rones</v>
       </c>
       <c r="C20">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D20">
         <v>38000</v>
@@ -847,7 +847,7 @@
         <v>Cervezas</v>
       </c>
       <c r="C23">
-        <v>146</v>
+        <v>96</v>
       </c>
       <c r="D23">
         <v>10000</v>
@@ -867,7 +867,7 @@
         <v>Cervezas</v>
       </c>
       <c r="C24">
-        <v>115</v>
+        <v>183</v>
       </c>
       <c r="D24">
         <v>10000</v>
@@ -887,10 +887,10 @@
         <v>Cervezas</v>
       </c>
       <c r="C25">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D25">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="E25" t="str">
         <v>10/2/2026</v>
@@ -907,7 +907,7 @@
         <v>Cervezas</v>
       </c>
       <c r="C26">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D26">
         <v>10000</v>
@@ -967,7 +967,7 @@
         <v>Hidratantes</v>
       </c>
       <c r="C29">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D29">
         <v>6000</v>
@@ -987,7 +987,7 @@
         <v>Hidratantes</v>
       </c>
       <c r="C30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D30">
         <v>10000</v>
@@ -1007,7 +1007,7 @@
         <v>Gaseosas</v>
       </c>
       <c r="C31">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D31">
         <v>5000</v>
@@ -1027,7 +1027,7 @@
         <v>Otros</v>
       </c>
       <c r="C32">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D32">
         <v>5000</v>
@@ -1047,7 +1047,7 @@
         <v>Otros</v>
       </c>
       <c r="C33">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D33">
         <v>3000</v>
@@ -1067,7 +1067,7 @@
         <v>Gaseosas</v>
       </c>
       <c r="C34">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D34">
         <v>5000</v>
@@ -1107,7 +1107,7 @@
         <v>Cervezas</v>
       </c>
       <c r="C36">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D36">
         <v>12000</v>
@@ -1127,7 +1127,7 @@
         <v>Gaseosas</v>
       </c>
       <c r="C37">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D37">
         <v>5000</v>
@@ -1147,7 +1147,7 @@
         <v>Gaseosas</v>
       </c>
       <c r="C38">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D38">
         <v>5000</v>
@@ -1207,7 +1207,7 @@
         <v>Otros</v>
       </c>
       <c r="C41">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D41">
         <v>3000</v>

--- a/data/inventario.xlsx
+++ b/data/inventario.xlsx
@@ -467,7 +467,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D4">
         <v>108000</v>
@@ -487,7 +487,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D5">
         <v>110000</v>
@@ -507,7 +507,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C6">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="D6">
         <v>56000</v>
@@ -527,7 +527,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C7">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D7">
         <v>88000</v>
@@ -547,7 +547,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C8">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D8">
         <v>36000</v>
@@ -567,7 +567,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D9">
         <v>100000</v>
@@ -587,7 +587,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C10">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="D10">
         <v>54000</v>
@@ -607,7 +607,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C11">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D11">
         <v>86000</v>
@@ -627,7 +627,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C12">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12">
         <v>36000</v>
@@ -647,7 +647,7 @@
         <v>Rones</v>
       </c>
       <c r="C13">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13">
         <v>88000</v>
@@ -687,7 +687,7 @@
         <v>Rones</v>
       </c>
       <c r="C15">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D15">
         <v>78000</v>
@@ -767,7 +767,7 @@
         <v>Rones</v>
       </c>
       <c r="C19">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D19">
         <v>104000</v>
@@ -847,10 +847,10 @@
         <v>Cervezas</v>
       </c>
       <c r="C23">
-        <v>96</v>
+        <v>209</v>
       </c>
       <c r="D23">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="E23" t="str">
         <v>10/2/2026</v>
@@ -867,10 +867,10 @@
         <v>Cervezas</v>
       </c>
       <c r="C24">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="D24">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="E24" t="str">
         <v>10/2/2026</v>
@@ -887,7 +887,7 @@
         <v>Cervezas</v>
       </c>
       <c r="C25">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D25">
         <v>12000</v>
@@ -907,10 +907,10 @@
         <v>Cervezas</v>
       </c>
       <c r="C26">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="D26">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="E26" t="str">
         <v>10/2/2026</v>
@@ -967,7 +967,7 @@
         <v>Hidratantes</v>
       </c>
       <c r="C29">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D29">
         <v>6000</v>
@@ -987,7 +987,7 @@
         <v>Hidratantes</v>
       </c>
       <c r="C30">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D30">
         <v>10000</v>
@@ -1007,7 +1007,7 @@
         <v>Gaseosas</v>
       </c>
       <c r="C31">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D31">
         <v>5000</v>
@@ -1027,7 +1027,7 @@
         <v>Otros</v>
       </c>
       <c r="C32">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D32">
         <v>5000</v>
@@ -1047,7 +1047,7 @@
         <v>Otros</v>
       </c>
       <c r="C33">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D33">
         <v>3000</v>
@@ -1067,7 +1067,7 @@
         <v>Gaseosas</v>
       </c>
       <c r="C34">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D34">
         <v>5000</v>
@@ -1127,7 +1127,7 @@
         <v>Gaseosas</v>
       </c>
       <c r="C37">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D37">
         <v>5000</v>
@@ -1147,7 +1147,7 @@
         <v>Gaseosas</v>
       </c>
       <c r="C38">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="D38">
         <v>5000</v>
@@ -1207,7 +1207,7 @@
         <v>Otros</v>
       </c>
       <c r="C41">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D41">
         <v>3000</v>

--- a/data/inventario.xlsx
+++ b/data/inventario.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F45"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,7 +427,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>122000</v>
@@ -447,7 +447,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C3">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>70000</v>
@@ -467,7 +467,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>108000</v>
@@ -487,7 +487,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C5">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D5">
         <v>110000</v>
@@ -507,7 +507,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C6">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="D6">
         <v>56000</v>
@@ -527,7 +527,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C7">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D7">
         <v>88000</v>
@@ -567,7 +567,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C9">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>100000</v>
@@ -587,7 +587,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C10">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D10">
         <v>54000</v>
@@ -607,7 +607,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C11">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D11">
         <v>86000</v>
@@ -627,7 +627,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C12">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D12">
         <v>36000</v>
@@ -687,7 +687,7 @@
         <v>Rones</v>
       </c>
       <c r="C15">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D15">
         <v>78000</v>
@@ -707,7 +707,7 @@
         <v>Rones</v>
       </c>
       <c r="C16">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D16">
         <v>132000</v>
@@ -727,7 +727,7 @@
         <v>Rones</v>
       </c>
       <c r="C17">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D17">
         <v>110000</v>
@@ -747,7 +747,7 @@
         <v>Rones</v>
       </c>
       <c r="C18">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D18">
         <v>68000</v>
@@ -767,7 +767,7 @@
         <v>Rones</v>
       </c>
       <c r="C19">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D19">
         <v>104000</v>
@@ -847,10 +847,10 @@
         <v>Cervezas</v>
       </c>
       <c r="C23">
-        <v>209</v>
+        <v>163</v>
       </c>
       <c r="D23">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="E23" t="str">
         <v>10/2/2026</v>
@@ -867,10 +867,10 @@
         <v>Cervezas</v>
       </c>
       <c r="C24">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="D24">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="E24" t="str">
         <v>10/2/2026</v>
@@ -907,10 +907,10 @@
         <v>Cervezas</v>
       </c>
       <c r="C26">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D26">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="E26" t="str">
         <v>10/2/2026</v>
@@ -967,7 +967,7 @@
         <v>Hidratantes</v>
       </c>
       <c r="C29">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D29">
         <v>6000</v>
@@ -987,7 +987,7 @@
         <v>Hidratantes</v>
       </c>
       <c r="C30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D30">
         <v>10000</v>
@@ -1007,7 +1007,7 @@
         <v>Gaseosas</v>
       </c>
       <c r="C31">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D31">
         <v>5000</v>
@@ -1067,7 +1067,7 @@
         <v>Gaseosas</v>
       </c>
       <c r="C34">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="D34">
         <v>5000</v>
@@ -1107,7 +1107,7 @@
         <v>Cervezas</v>
       </c>
       <c r="C36">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D36">
         <v>12000</v>
@@ -1127,7 +1127,7 @@
         <v>Gaseosas</v>
       </c>
       <c r="C37">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D37">
         <v>5000</v>
@@ -1147,7 +1147,7 @@
         <v>Gaseosas</v>
       </c>
       <c r="C38">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D38">
         <v>5000</v>
@@ -1207,7 +1207,7 @@
         <v>Otros</v>
       </c>
       <c r="C41">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D41">
         <v>3000</v>
@@ -1247,7 +1247,7 @@
         <v>Ingresos Cafeteria</v>
       </c>
       <c r="C43">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -1279,9 +1279,29 @@
         <v>0</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Amarillo Edicion Yeison Jimenez</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Aguardientes</v>
+      </c>
+      <c r="C45">
+        <v>12</v>
+      </c>
+      <c r="D45">
+        <v>130000</v>
+      </c>
+      <c r="E45" t="str">
+        <v>4/26/2026</v>
+      </c>
+      <c r="F45">
+        <v>48800</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F44"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F45"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/inventario.xlsx
+++ b/data/inventario.xlsx
@@ -427,7 +427,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D2">
         <v>122000</v>
@@ -447,7 +447,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D3">
         <v>70000</v>
@@ -467,7 +467,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D4">
         <v>108000</v>
@@ -487,7 +487,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C5">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D5">
         <v>110000</v>
@@ -507,7 +507,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C6">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="D6">
         <v>56000</v>
@@ -527,7 +527,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7">
         <v>88000</v>
@@ -547,7 +547,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D8">
         <v>36000</v>
@@ -587,7 +587,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C10">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D10">
         <v>54000</v>
@@ -627,7 +627,7 @@
         <v>Aguardientes</v>
       </c>
       <c r="C12">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D12">
         <v>36000</v>
@@ -687,7 +687,7 @@
         <v>Rones</v>
       </c>
       <c r="C15">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D15">
         <v>78000</v>
@@ -787,7 +787,7 @@
         <v>Rones</v>
       </c>
       <c r="C20">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D20">
         <v>38000</v>
@@ -847,10 +847,10 @@
         <v>Cervezas</v>
       </c>
       <c r="C23">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="D23">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="E23" t="str">
         <v>10/2/2026</v>
@@ -867,10 +867,10 @@
         <v>Cervezas</v>
       </c>
       <c r="C24">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="D24">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="E24" t="str">
         <v>10/2/2026</v>
@@ -887,7 +887,7 @@
         <v>Cervezas</v>
       </c>
       <c r="C25">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D25">
         <v>12000</v>
@@ -907,10 +907,10 @@
         <v>Cervezas</v>
       </c>
       <c r="C26">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D26">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="E26" t="str">
         <v>10/2/2026</v>
@@ -967,7 +967,7 @@
         <v>Hidratantes</v>
       </c>
       <c r="C29">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D29">
         <v>6000</v>
@@ -987,7 +987,7 @@
         <v>Hidratantes</v>
       </c>
       <c r="C30">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D30">
         <v>10000</v>
@@ -1007,7 +1007,7 @@
         <v>Gaseosas</v>
       </c>
       <c r="C31">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D31">
         <v>5000</v>
@@ -1027,7 +1027,7 @@
         <v>Otros</v>
       </c>
       <c r="C32">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D32">
         <v>5000</v>
@@ -1047,7 +1047,7 @@
         <v>Otros</v>
       </c>
       <c r="C33">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D33">
         <v>3000</v>
@@ -1067,7 +1067,7 @@
         <v>Gaseosas</v>
       </c>
       <c r="C34">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D34">
         <v>5000</v>
@@ -1107,7 +1107,7 @@
         <v>Cervezas</v>
       </c>
       <c r="C36">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D36">
         <v>12000</v>
@@ -1127,7 +1127,7 @@
         <v>Gaseosas</v>
       </c>
       <c r="C37">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D37">
         <v>5000</v>
@@ -1147,7 +1147,7 @@
         <v>Gaseosas</v>
       </c>
       <c r="C38">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D38">
         <v>5000</v>
@@ -1207,7 +1207,7 @@
         <v>Otros</v>
       </c>
       <c r="C41">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D41">
         <v>3000</v>
@@ -1227,7 +1227,7 @@
         <v>Ingresos Barra</v>
       </c>
       <c r="C42">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -1247,7 +1247,7 @@
         <v>Ingresos Cafeteria</v>
       </c>
       <c r="C43">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="D43">
         <v>0</v>
